--- a/Przykladowa_lista_dla_konwojentow.xlsx
+++ b/Przykladowa_lista_dla_konwojentow.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan konwoju" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plan konwoju'!$A$1:$D$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plan konwoju'!$A$1:$C$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,13 +430,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -452,11 +451,6 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Lokalizacja</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
           <t>Adres</t>
         </is>
       </c>
@@ -472,11 +466,6 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Strefa 1</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
           <t>ul. Żeromskiego 3</t>
         </is>
       </c>
@@ -492,11 +481,6 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Strefa 4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
           <t>ul. 25 Czerwca 10</t>
         </is>
       </c>
@@ -512,11 +496,6 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Strefa 3</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
           <t>ul. Malczewskiego 17</t>
         </is>
       </c>
@@ -532,11 +511,6 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Strefa 2</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
           <t>ul. Struga 24</t>
         </is>
       </c>
@@ -552,17 +526,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Strefa 1</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
           <t>ul. Warszawska 3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D6"/>
+  <autoFilter ref="A1:C6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>